--- a/medical_application_forms/038_neurological_exam_form--medical_application_forms.xlsx
+++ b/medical_application_forms/038_neurological_exam_form--medical_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1211,17 +1211,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cranial_meningitis_choices</t>
+          <t>cranial_muscle_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>meningocele</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Meningocele</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>abnormal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Abnormal</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>abnormal</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Abnormal</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cranial_muscle_choices</t>
+          <t>cranial_nerve_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>weak</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1301,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>weak</t>
+          <t>abnormal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Abnormal</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cranial_nerve_choices</t>
+          <t>cranial_pupils_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>abnormal</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Abnormal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>abnormal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Abnormal</t>
         </is>
       </c>
     </row>
@@ -1352,29 +1352,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>abnormal</t>
+          <t>dilated</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Abnormal</t>
+          <t>Dilated</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cranial_pupils_choices</t>
+          <t>cranial_sensory_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dilated</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dilated</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1386,29 +1386,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>abnormal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Abnormal</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cranial_sensory_choices</t>
+          <t>extraocular_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>abnormal</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Abnormal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1420,29 +1420,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>abnormal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Abnormal</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>extraocular_choices</t>
+          <t>face_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>abnormal</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Abnormal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1454,29 +1454,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>abnormal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Abnormal</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>face_choices</t>
+          <t>head_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>abnormal</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Abnormal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>abnormal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Abnormal</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>head_choices</t>
+          <t>hearing_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>abnormal</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Abnormal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>abnormal</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Abnormal</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>abnormal</t>
+          <t>decreased</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Abnormal</t>
+          <t>Decreased</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1556,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>decreased</t>
+          <t>increased</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Decreased</t>
+          <t>Increased</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hearing_choices</t>
+          <t>mental_status_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>increased</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Increased</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>altered</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Altered</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1607,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>altered</t>
+          <t>decreased</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Altered</t>
+          <t>Decreased</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mental_status_choices</t>
+          <t>motor_response_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>decreased</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Decreased</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1641,19 +1641,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>abnormal</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Abnormal</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>motor_response_choices</t>
+          <t>motor_strength_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1670,7 +1670,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>motor_response_choices</t>
+          <t>motor_strength_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>motor_strength_choices</t>
+          <t>muscle_tone_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1704,7 +1704,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>motor_strength_choices</t>
+          <t>muscle_tone_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1726,53 +1726,53 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>decreased</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Decreased</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>muscle_tone_choices</t>
+          <t>reflexes_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>abnormal</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Abnormal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>muscle_tone_choices</t>
+          <t>reflexes_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>decreased</t>
+          <t>abnormal</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Decreased</t>
+          <t>Abnormal</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>reflexes_choices</t>
+          <t>sensiblity_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1789,7 +1789,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>reflexes_choices</t>
+          <t>sensiblity_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1806,7 +1806,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>sensiblity_choices</t>
+          <t>speech_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>sensiblity_choices</t>
+          <t>speech_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>speech_choices</t>
+          <t>vision_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>speech_choices</t>
+          <t>vision_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>vision_choices</t>
+          <t>cranial_vital_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>vision_choices</t>
+          <t>cranial_vital_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1908,7 +1908,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cranial_vital_choices</t>
+          <t>general_appearance_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1925,7 +1925,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>cranial_vital_choices</t>
+          <t>general_appearance_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1942,7 +1942,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>general_appearance_choices</t>
+          <t>general_condition_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1959,7 +1959,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>general_appearance_choices</t>
+          <t>general_condition_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1976,7 +1976,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>general_condition_choices</t>
+          <t>general_moving_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>general_condition_choices</t>
+          <t>general_moving_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2015,53 +2015,53 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>decreased</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Decreased</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>general_moving_choices</t>
+          <t>general_posture_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>abnormal</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Abnormal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>general_moving_choices</t>
+          <t>general_posture_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>decreased</t>
+          <t>abnormal</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Decreased</t>
+          <t>Abnormal</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>general_posture_choices</t>
+          <t>general_sensory_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2078,7 +2078,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>general_posture_choices</t>
+          <t>general_sensory_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2087,40 +2087,6 @@
         </is>
       </c>
       <c r="C58" t="inlineStr">
-        <is>
-          <t>Abnormal</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>general_sensory_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>general_sensory_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>abnormal</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
         <is>
           <t>Abnormal</t>
         </is>
